--- a/Lab03_Geography2.xlsx
+++ b/Lab03_Geography2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsofteur-my.sharepoint.com/personal/kpochodaj_microsoft_com/Documents/Documents/_PARA/Resources/VBD/Fabric/Upskilling/Power BI/Advanced/2 ADV Lab Assets/M01L01Lab03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9A1D769-DF2E-4780-868F-E2C67813A4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{B9A1D769-DF2E-4780-868F-E2C67813A4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE2C4D1B-4FF1-45BE-BEBE-49655CDED011}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{873C864E-8568-45BC-A9AA-52B5CA925431}"/>
   </bookViews>
@@ -16392,11 +16392,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Classified as Microsoft Confidential</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{87ba5c36-b7cf-4793-bbc2-bd5b3a9f95ca}" enabled="1" method="Privileged" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
+  <clbl:label id="{1a19d03a-48bc-4359-8038-5b5f6d5847c3}" enabled="1" method="Privileged" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" removed="0"/>
 </clbl:labelList>
 </file>